--- a/documentation/Coupa sample invoice.xlsx
+++ b/documentation/Coupa sample invoice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FurJes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758A9390-9222-41D5-B2BB-82A93A393DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7922E5B-8E41-4CE4-B9EA-3F28956937EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Final" sheetId="7" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="259">
   <si>
     <t>Invoice</t>
   </si>
@@ -807,6 +807,9 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>&lt;&lt;Approver Name&gt;&gt;</t>
   </si>
 </sst>
 </file>
@@ -1149,168 +1152,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE8D1E1-8A4F-4D48-917D-C3ED027C1095}">
   <dimension ref="A1:FU4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="31" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="40.1796875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="33.1796875" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="24.453125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="24" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="84" max="84" width="31" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="27" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="30.7265625" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="93" max="94" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="93" max="94" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="99" max="99" width="14" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="105" max="106" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="33.1796875" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="112" max="113" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="105" max="106" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="112" max="113" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="118" max="118" width="15" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="122" max="122" width="24" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="45.26953125" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="129" max="129" width="24" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="138" max="138" width="41" bestFit="1" customWidth="1"/>
     <col min="139" max="140" width="26" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="146" max="146" width="12" bestFit="1" customWidth="1"/>
     <col min="147" max="147" width="20" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="30.7265625" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="151" max="151" width="21" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="156" max="164" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="156" max="164" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="165" max="165" width="14" bestFit="1" customWidth="1"/>
-    <col min="166" max="167" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="168" max="169" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="170" max="171" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="172" max="173" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="174" max="174" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="175" max="175" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="166" max="167" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="168" max="169" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="170" max="171" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="172" max="173" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="174" max="174" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="175" max="175" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="177" max="177" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:177" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1843,7 +1846,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:177" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>159</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" spans="1:177" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2089,6 +2092,9 @@
       <c r="K3" t="s">
         <v>171</v>
       </c>
+      <c r="T3" t="s">
+        <v>258</v>
+      </c>
       <c r="V3" t="s">
         <v>184</v>
       </c>
@@ -2099,7 +2105,7 @@
         <v>223680</v>
       </c>
     </row>
-    <row r="4" spans="1:177" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>159</v>
       </c>
@@ -2278,18 +2284,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2311,18 +2317,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E438901-CE8D-49FE-B81C-A0B07384508B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B002FF76-8BE9-4CC0-B770-F4F5C5D4CC3C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B002FF76-8BE9-4CC0-B770-F4F5C5D4CC3C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E438901-CE8D-49FE-B81C-A0B07384508B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
